--- a/artfynd/A 55218-2025 artfynd.xlsx
+++ b/artfynd/A 55218-2025 artfynd.xlsx
@@ -900,7 +900,7 @@
         <v>129688621</v>
       </c>
       <c r="B4" t="n">
-        <v>79166</v>
+        <v>79170</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 55218-2025 artfynd.xlsx
+++ b/artfynd/A 55218-2025 artfynd.xlsx
@@ -900,7 +900,7 @@
         <v>129688621</v>
       </c>
       <c r="B4" t="n">
-        <v>79170</v>
+        <v>79171</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 55218-2025 artfynd.xlsx
+++ b/artfynd/A 55218-2025 artfynd.xlsx
@@ -900,7 +900,7 @@
         <v>129688621</v>
       </c>
       <c r="B4" t="n">
-        <v>79171</v>
+        <v>79176</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 55218-2025 artfynd.xlsx
+++ b/artfynd/A 55218-2025 artfynd.xlsx
@@ -900,7 +900,7 @@
         <v>129688621</v>
       </c>
       <c r="B4" t="n">
-        <v>79176</v>
+        <v>79179</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 55218-2025 artfynd.xlsx
+++ b/artfynd/A 55218-2025 artfynd.xlsx
@@ -900,7 +900,7 @@
         <v>129688621</v>
       </c>
       <c r="B4" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 55218-2025 artfynd.xlsx
+++ b/artfynd/A 55218-2025 artfynd.xlsx
@@ -900,7 +900,7 @@
         <v>129688621</v>
       </c>
       <c r="B4" t="n">
-        <v>79182</v>
+        <v>79183</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 55218-2025 artfynd.xlsx
+++ b/artfynd/A 55218-2025 artfynd.xlsx
@@ -900,7 +900,7 @@
         <v>129688621</v>
       </c>
       <c r="B4" t="n">
-        <v>79183</v>
+        <v>79184</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
